--- a/etf_holdings/2026-10-15_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-10-15_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -464,29 +464,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>00981A(385,000)、00407A(70,000)</t>
+          <t>00985A(22,000)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00403A(-250,000)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -499,24 +499,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>00985A(22,000)</t>
+          <t>00991A(20,000)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>00403A(-250,000)</t>
+          <t>00985A(-15,000)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -524,105 +524,15 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>00991A(20,000)</t>
+          <t>00991A(30,000)、00985A(15,000)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
-        <is>
-          <t>00985A(-15,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>欣興</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>00981A(217,000)、00985A(73,000)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>00991A(30,000)、00985A(15,000)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>台燿</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>00981A(199,000)、00403A(120,000)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/etf_holdings/2026-10-15_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-10-15_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -464,29 +464,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>00985A(22,000)</t>
+          <t>00981A(385,000)、00407A(70,000)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>00403A(-250,000)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -494,45 +494,15 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>00991A(20,000)</t>
+          <t>00981A(199,000)、00403A(120,000)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
-        <is>
-          <t>00985A(-15,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>00991A(30,000)、00985A(15,000)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
